--- a/Assets/Excels/PlayerData.xlsx
+++ b/Assets/Excels/PlayerData.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\a\T4-GitHub\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12288"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,10 +38,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Shars</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -51,13 +47,17 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stars</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -97,9 +97,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -381,84 +384,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>100</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>30</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>100</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>30</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>100</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>30</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0</v>
       </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
